--- a/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-009.xlsx
+++ b/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-009.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\DnaCalc\Foundation\research\runs\20260302-070309-excel-formula-language-pass2-pack-01\fixtures\formula_parse_pass2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FA20AC-7170-442D-8C32-7D14479A8E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9572D6F7-AB59-446D-A0CA-91BEA77BDF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{C79D2CD8-C3B7-4F30-98B6-BB88821A8F67}"/>
+    <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{25870475-4D69-48B6-806B-3DEC75EE4370}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -491,7 +491,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{427EBC6B-8392-4D23-B778-5ACEE6AD145D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825E227E-A25A-4270-B22D-454BFD047C4F}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
